--- a/data/input/preparation/ai_results/quality_reports/mizuno_disagreements_Information_valence_human.xlsx
+++ b/data/input/preparation/ai_results/quality_reports/mizuno_disagreements_Information_valence_human.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,27 +451,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JPN21M00-00</t>
+          <t>JPN21M09-00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>STAKE</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>neutral</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>STAKE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Neutral</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -483,7 +483,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JPN21M05-00</t>
+          <t>JPN22M05-00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -498,12 +498,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>STRAT</t>
+          <t>STAKE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -515,12 +515,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JPN21M09-00</t>
+          <t>JPN25M02-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>PERF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -530,303 +530,15 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>STRAT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>mizuno</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>JPN22M01-00</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CHALL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CHALL</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>mizuno</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>JPN22M05-00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>STRAT</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>STAKE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mizuno</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>JPN23M05-00</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>STRAT</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>PEOPLE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>mizuno</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>JPN24M01-00</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>STRAT</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>STRAT</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mizuno</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>JPN25M02-01</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PERF</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>STRAT</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>mizuno</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>JPN25M02-03</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PEOPLE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>STAKE</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mizuno</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>JPN25M04-01</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PEOPLE</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>PEOPLE</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>mizuno</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>JPN25M04-02</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CHALL</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>mizuno</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>JPN25M05-00</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>STRAT</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>STRAT</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
         <is>
           <t>mizuno</t>
         </is>
